--- a/out/MLP-Mamba1_repeat_3_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.137873157325433</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003087850468152901</v>
+        <v>-0.0002339981777789071</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.55983554350491</v>
+        <v>2.697653396640524</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC40" t="n">
-        <v>7.12517395032102</v>
+        <v>5.399476878590129</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5338132193761543</v>
+        <v>0.4045251604527417</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.628187056613684</v>
+        <v>3.507253180934592</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6674402158090327</v>
+        <v>0.505788017800277</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.137873157325433</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.429339042117581</v>
+        <v>4.114368411075403</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9567722214177415</v>
+        <v>0.725044724866763</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.675820260803341</v>
+        <v>5.058955493760499</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.023557107740903</v>
+        <v>0.7756542389041793</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.766233264758825</v>
+        <v>5.885273676060411</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.084763488968523</v>
+        <v>0.8220371528856829</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.91228206412217</v>
+        <v>6.753753217220179</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4895342531624715</v>
+        <v>0.370970744076211</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.805684170609595</v>
+        <v>6.672972966159398</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2364226693599036</v>
+        <v>0.179161913599167</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.788611394420764</v>
+        <v>6.660035157527415</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1126477503035147</v>
+        <v>0.08536531784029106</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.777297700012841</v>
+        <v>6.651461600210714</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0333767426441922</v>
+        <v>0.02529278501971256</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.137873157325433</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.731282943705352</v>
+        <v>6.6165916491596</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02207795110083229</v>
+        <v>0.01673023410948814</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.137873157325433</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.742043949127989</v>
+        <v>6.624746360877584</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01129769243397631</v>
+        <v>0.008560329297272027</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.742547509030059</v>
+        <v>6.6251267597802</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005777267317571653</v>
+        <v>0.00437700028436445</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.742796643046288</v>
+        <v>6.625314351244796</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002168773482149537</v>
+        <v>0.001641981579790178</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.741352542008661</v>
+        <v>6.624218751634797</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001179708583343353</v>
+        <v>0.0008926065032573595</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.741541974744717</v>
+        <v>6.624361133776996</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005656161045008799</v>
+        <v>0.0004273330931037306</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.137873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.741492749251726</v>
+        <v>6.624322595570184</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003482398871591795</v>
+        <v>0.000262635791942331</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.741623346095524</v>
+        <v>6.624420521350029</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001792570791898958</v>
+        <v>0.0001349942054180214</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.741634445126937</v>
+        <v>6.624427763938979</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.4918381770666e-05</v>
+        <v>6.293833289339209e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.137873157325433</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.741623879443726</v>
+        <v>6.624418528443705</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.256158699932203e-05</v>
+        <v>3.849097684393219e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.741644044651533</v>
+        <v>6.624432822545987</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.064344810800705e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.741633898277733</v>
+        <v>6.624423819968163</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.741625747166712</v>
+        <v>6.624416353391169</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.7416217393608</v>
+        <v>6.624412098212998</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.741615871918116</v>
+        <v>6.624406375933968</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.737873157325433</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.741610802562747</v>
+        <v>6.624401306578599</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.741606437588779</v>
+        <v>6.62439694160463</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.741607528835235</v>
+        <v>6.624398032851087</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.741606839228099</v>
+        <v>6.624397343243951</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.741606869540501</v>
+        <v>6.624397373556353</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.137873157325433</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.74160668008799</v>
+        <v>6.624397184103842</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.741606733134695</v>
+        <v>6.624397237150546</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.741606786181396</v>
+        <v>6.624397290197249</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.741606748290895</v>
+        <v>6.624397252306746</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.741606619463189</v>
+        <v>6.62439712347904</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.74160647547928</v>
+        <v>6.624396979495132</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.741606316339173</v>
+        <v>6.624396820355024</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.741606369385876</v>
+        <v>6.624396873401727</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.741606316339173</v>
+        <v>6.624396820355024</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.741606316339173</v>
+        <v>6.624396820355024</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.741606134464764</v>
+        <v>6.624396638480615</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.741606301182973</v>
+        <v>6.624396805198823</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.741606498213581</v>
+        <v>6.624397002229434</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.741606339073474</v>
+        <v>6.624396843089325</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.741606376963976</v>
+        <v>6.624396880979827</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.741606573994586</v>
+        <v>6.624397078010437</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.741606551260285</v>
+        <v>6.624397055276136</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.741606399698275</v>
+        <v>6.624396903714127</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.741606323917273</v>
+        <v>6.624396827933125</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.741606422432577</v>
+        <v>6.62439692644843</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.741606430010679</v>
+        <v>6.62439693402653</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.741606695244192</v>
+        <v>6.624397199260044</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.741606399698275</v>
+        <v>6.624396903714127</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.741606642197489</v>
+        <v>6.62439714621334</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.741606725556593</v>
+        <v>6.624397229572446</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.741606558838384</v>
+        <v>6.624397062854237</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.741606748290895</v>
+        <v>6.624397252306746</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.741606399698275</v>
+        <v>6.624396903714127</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.741606195089565</v>
+        <v>6.624396699105417</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.741606308761071</v>
+        <v>6.624396812776923</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.741606323917273</v>
+        <v>6.624396827933125</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.741606088996161</v>
+        <v>6.624396593012013</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.741606149620964</v>
+        <v>6.624396653636815</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.741606020793258</v>
+        <v>6.624396524809108</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.741606157199064</v>
+        <v>6.624396661214916</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.741606331495372</v>
+        <v>6.624396835511225</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.74160647547928</v>
+        <v>6.624396979495132</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.741606308761071</v>
+        <v>6.624396812776923</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.741606301182973</v>
+        <v>6.624396805198823</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.741606013215156</v>
+        <v>6.624396517231008</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.737873157325433</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.741606028371356</v>
+        <v>6.624396532387209</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.74160625571437</v>
+        <v>6.624396759730221</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.737873157325433</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.741606240558168</v>
+        <v>6.624396744574019</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.741606346651574</v>
+        <v>6.624396850667425</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.741606073839959</v>
+        <v>6.624396577855811</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.737873157325433</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.741606172355265</v>
+        <v>6.624396676371116</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.741606323917273</v>
+        <v>6.624396827933125</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.741606339073474</v>
+        <v>6.624396843089325</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.741606316339173</v>
+        <v>6.624396820355024</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.757166170459627</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.741606399698275</v>
+        <v>6.624396903714127</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.045076465039655</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.741606498213581</v>
+        <v>6.624397002229434</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.741606331495372</v>
+        <v>6.624396835511225</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.741606316339173</v>
+        <v>6.624396820355024</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.741606286026769</v>
+        <v>6.624396790042622</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.157166170459627</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.74160627087057</v>
+        <v>6.624396774886422</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.741606308761071</v>
+        <v>6.624396812776923</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.741606323917273</v>
+        <v>6.624396827933125</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.103979445500941</v>
+        <v>-1.645076465039655</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.741606316339173</v>
+        <v>6.624396820355024</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_3_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-0.391300191200645</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.137873157325433</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.737873157325433</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003087850468152901</v>
+        <v>-0.0001266670576847391</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.55983554350491</v>
+        <v>1.460284099854351</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC40" t="n">
-        <v>7.12517395032102</v>
+        <v>2.922825535391437</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5338132193761543</v>
+        <v>0.2189760920825108</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.628187056613684</v>
+        <v>1.898533763002692</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6674402158090327</v>
+        <v>0.2737913653157056</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.137873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.429339042117581</v>
+        <v>2.227175244685032</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9567722214177415</v>
+        <v>0.3924786237514393</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.675820260803341</v>
+        <v>2.738495851644693</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.023557107740903</v>
+        <v>0.4198743853326085</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.766233264758825</v>
+        <v>3.185795632386086</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.084763488968523</v>
+        <v>0.4449822188505853</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.91228206412217</v>
+        <v>3.655918237189387</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4895342531624715</v>
+        <v>0.2008121992432473</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.805684170609595</v>
+        <v>3.612190494385437</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2364226693599036</v>
+        <v>0.09698375696588786</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.788611394420764</v>
+        <v>3.605187012100453</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1126477503035147</v>
+        <v>0.04620987280399896</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.777297700012841</v>
+        <v>3.600545982193861</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0333767426441922</v>
+        <v>0.01369085097670864</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.137873157325433</v>
+        <v>0.8906895700914115</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.731282943705352</v>
+        <v>3.581669401097494</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02207795110083229</v>
+        <v>0.009053802069990284</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.137873157325433</v>
+        <v>0.8906895700914115</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.742043949127989</v>
+        <v>3.586081396910303</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01129769243397631</v>
+        <v>0.00463139651335391</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.742547509030059</v>
+        <v>3.586285023034047</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005777267317571653</v>
+        <v>0.002366695995856339</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.742796643046288</v>
+        <v>3.586384283188654</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002168773482149537</v>
+        <v>0.0008866104324415577</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.741352542008661</v>
+        <v>3.585788761167635</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001179708583343353</v>
+        <v>0.0004809285206053169</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.741541974744717</v>
+        <v>3.585863579288043</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005656161045008799</v>
+        <v>0.0002294453354147069</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.137873157325433</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.741492749251726</v>
+        <v>3.585840408646773</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003482398871591795</v>
+        <v>0.0001396414022629509</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.741623346095524</v>
+        <v>3.585891121040894</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001792570791898958</v>
+        <v>7.117331765392342e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.741634445126937</v>
+        <v>3.585892757709318</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.4918381770666e-05</v>
+        <v>3.196644583905158e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.137873157325433</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.741623879443726</v>
+        <v>3.585885469595108</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.256158699932203e-05</v>
+        <v>1.802463479972881e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.741644044651533</v>
+        <v>3.585890816067946</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.064344810800705e-05</v>
+        <v>5.490501498730158e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.741633898277733</v>
+        <v>3.585883643563684</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.741625747166712</v>
+        <v>3.585877273243131</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.7416217393608</v>
+        <v>3.585872687333599</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.741615871918116</v>
+        <v>3.58586725420213</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.741610802562747</v>
+        <v>3.585862207581063</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.741606437588779</v>
+        <v>3.585862525861279</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.741607528835235</v>
+        <v>3.585863617107736</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.741606839228099</v>
+        <v>3.5858629275006</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.741606869540501</v>
+        <v>3.585862957813002</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.137873157325433</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.74160668008799</v>
+        <v>3.585862768360492</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.741606733134695</v>
+        <v>3.585862821407195</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.741606786181396</v>
+        <v>3.585862874453897</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.741606748290895</v>
+        <v>3.585862836563396</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.741606619463189</v>
+        <v>3.585862707735688</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.74160647547928</v>
+        <v>3.585862563751781</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.741606316339173</v>
+        <v>3.585862404611673</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.741606369385876</v>
+        <v>3.585862457658376</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.741606316339173</v>
+        <v>3.585862404611673</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.741606316339173</v>
+        <v>3.585862404611673</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.741606134464764</v>
+        <v>3.585862222737264</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.741606301182973</v>
+        <v>3.585862389455472</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.741606498213581</v>
+        <v>3.585862586486082</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.741606339073474</v>
+        <v>3.585862427345974</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.737873157325433</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.741606376963976</v>
+        <v>3.585862465236476</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.741606573994586</v>
+        <v>3.585862662267086</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.741606551260285</v>
+        <v>3.585862639532785</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.741606399698275</v>
+        <v>3.585862487970777</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.741606323917273</v>
+        <v>3.585862412189773</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.741606422432577</v>
+        <v>3.585862510705079</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.737873157325433</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.741606430010679</v>
+        <v>3.585862518283179</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.741606695244192</v>
+        <v>3.585862783516693</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.741606399698275</v>
+        <v>3.585862487970777</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.741606642197489</v>
+        <v>3.585862730469989</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.741606725556593</v>
+        <v>3.585862813829094</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>2.737873157325433</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.741606558838384</v>
+        <v>3.585862647110886</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.741606748290895</v>
+        <v>3.585862836563396</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.741606399698275</v>
+        <v>3.585862487970777</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.741606195089565</v>
+        <v>3.585862283362066</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.741606308761071</v>
+        <v>3.585862397033572</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.741606323917273</v>
+        <v>3.585862412189773</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.741606088996161</v>
+        <v>3.585862177268662</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.741606149620964</v>
+        <v>3.585862237893464</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.741606020793258</v>
+        <v>3.585862109065757</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.737873157325433</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.741606157199064</v>
+        <v>3.585862245471565</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.741606331495372</v>
+        <v>3.585862419767873</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-0.391300191200645</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.74160647547928</v>
+        <v>3.585862563751781</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.391300191200645</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.741606308761071</v>
+        <v>3.585862397033572</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.741606301182973</v>
+        <v>3.585862389455472</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.741606013215156</v>
+        <v>3.585862101487657</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.737873157325433</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.741606028371356</v>
+        <v>3.585862116643858</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5039794455009405</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.74160625571437</v>
+        <v>3.58586234398687</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.737873157325433</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.741606240558168</v>
+        <v>3.585862328830669</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.741606346651574</v>
+        <v>3.585862434924075</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.741606073839959</v>
+        <v>3.58586216211246</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.737873157325433</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.741606172355265</v>
+        <v>3.585862260627765</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5039794455009405</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.741606323917273</v>
+        <v>3.585862412189773</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5039794455009405</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.741606339073474</v>
+        <v>3.585862427345974</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.741606316339173</v>
+        <v>3.585862404611673</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.741606399698275</v>
+        <v>3.585862487970777</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.741606498213581</v>
+        <v>3.585862586486082</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.741606331495372</v>
+        <v>3.585862419767873</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.741606316339173</v>
+        <v>3.585862404611673</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.741606286026769</v>
+        <v>3.585862374299271</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.74160627087057</v>
+        <v>3.585862359143071</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.741606308761071</v>
+        <v>3.585862397033572</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.741606323917273</v>
+        <v>3.585862412189773</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.591300191200645</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.741606316339173</v>
+        <v>3.585862404611673</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_3_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4303023219108582</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.58</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4540941417217255</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4376072883605957</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.3832265436649323</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4652973711490631</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4318720400333405</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4190527200698853</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3887898027896881</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4540854692459106</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4122450053691864</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4209644496440887</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4131742417812347</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4808005392551422</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3757018148899078</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.37617427110672</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4129667282104492</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.473054438829422</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4047074317932129</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4316766262054443</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5506709218025208</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.090689570091412</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.568362832069397</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.83168445073744</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.6086592078208923</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.090689570091412</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.414949357509613</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4448352158069611</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.391300191200645</v>
+        <v>0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4428650140762329</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4134869277477264</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4004087448120117</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5672252178192139</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3919841349124908</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4392345547676086</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4149449169635773</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3415319919586182</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4548394680023193</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4698078036308289</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1496946894453832</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.6041152477264404</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.090689570091412</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.7457963824272156</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.090689570091412</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4919728934764862</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.090689570091412</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5806690454483032</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0001266670576847391</v>
+        <v>-0.0001442297056872631</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>1.460284099854351</v>
+        <v>1.662755492955732</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.3628858327865601</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>2.922825535391437</v>
+        <v>3.328081305828174</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.2189760920825108</v>
+        <v>0.2493376033478721</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.49091637134552</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.16</v>
       </c>
       <c r="JC41" t="n">
-        <v>1.898533763002692</v>
+        <v>2.161769372984634</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.2737913653157056</v>
+        <v>0.3117531333942921</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5133123993873596</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.090689570091412</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
-        <v>2.227175244685032</v>
+        <v>2.535977632975608</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.3924786237514393</v>
+        <v>0.446896638262141</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6741918921470642</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.83168445073744</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>2.738495851644693</v>
+        <v>3.118193712197221</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.4198743853326085</v>
+        <v>0.4780908817504419</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.7892181277275085</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.83168445073744</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>3.185795632386086</v>
+        <v>3.627512157246003</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4449822188505853</v>
+        <v>0.5066799709751724</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7580748796463013</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.83168445073744</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>3.655918237189387</v>
+        <v>4.162817394577987</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.2008121992432473</v>
+        <v>0.2286545814118022</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.621149480342865</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.090689570091412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>3.612190494385437</v>
+        <v>4.113026870119093</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.09698375696588786</v>
+        <v>0.110429711811827</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.414670318365097</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.3496946894453832</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>3.605187012100453</v>
+        <v>4.105052370426346</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.04620987280399896</v>
+        <v>0.05261708287207957</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.1608821600675583</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>3.600545982193861</v>
+        <v>4.099767840511219</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01369085097670864</v>
+        <v>0.01558948000753997</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.570720911026001</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.8906895700914115</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.581669401097494</v>
+        <v>4.078274628887007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.009053802069990284</v>
+        <v>0.01031015333330494</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5038540959358215</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8906895700914115</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>3.586081396910303</v>
+        <v>4.083299178444027</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00463139651335391</v>
+        <v>0.005274903160156426</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.2761980295181274</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>3.586285023034047</v>
+        <v>4.083531734850594</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002366695995856339</v>
+        <v>0.002695874514805839</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3609869778156281</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.586384283188654</v>
+        <v>4.083645439858524</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008866104324415577</v>
+        <v>0.001009982673942385</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4447287023067474</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>3.585788761167635</v>
+        <v>4.082968241838502</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004809285206053169</v>
+        <v>0.0005485790107405222</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4263668358325958</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.585863579288043</v>
+        <v>4.083054094460991</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0002294453354147069</v>
+        <v>0.00026123453343704</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.5437252521514893</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.585840408646773</v>
+        <v>4.083028429691553</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0001396414022629509</v>
+        <v>0.0001603044597290868</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4825732707977295</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.1496946894453832</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.585891121040894</v>
+        <v>4.083086884481966</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>7.117331765392342e-05</v>
+        <v>8.146700922877794e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.321798712015152</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1496946894453832</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.585892757709318</v>
+        <v>4.083089417997475</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>3.196644583905158e-05</v>
+        <v>3.696191149297746e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.8801813721656799</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.585885469595108</v>
+        <v>4.083081820678642</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.802463479972881e-05</v>
+        <v>2.186207393301694e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.4378393590450287</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.3496946894453832</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.585890816067946</v>
+        <v>4.083088564442286</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>5.490501498730158e-06</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.301520973443985</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.585883643563684</v>
+        <v>4.083081163178829</v>
       </c>
     </row>
     <row r="61">
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.4835888147354126</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.585877273243131</v>
+        <v>4.083074656452469</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-2.77474353817759e-06</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.280401736497879</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.585872687333599</v>
+        <v>4.083070152549514</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3616936206817627</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.58586725420213</v>
+        <v>4.083064719418045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.7170830965042114</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.090689570091412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.585862207581063</v>
+        <v>4.083059672796978</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9131059050559998</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.83168445073744</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.585862525861279</v>
+        <v>4.083059991077194</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.9469486474990845</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.090689570091412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.585863617107736</v>
+        <v>4.083061082323651</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.2820963859558105</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.5858629275006</v>
+        <v>4.083060392716515</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.2045919299125671</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.585862957813002</v>
+        <v>4.083060423028917</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5172472596168518</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.585862768360492</v>
+        <v>4.083060233576407</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4815314412117004</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.585862821407195</v>
+        <v>4.08306028662311</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2886600196361542</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.585862874453897</v>
+        <v>4.083060339669813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2943706810474396</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.585862836563396</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2577203512191772</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.585862707735688</v>
+        <v>4.083060172951603</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.2921161651611328</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.585862563751781</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3960876762866974</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.585862404611673</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.356293112039566</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.585862457658376</v>
+        <v>4.08305992287429</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3693419396877289</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.585862404611673</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.2237703800201416</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.585862404611673</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.6212947964668274</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.090689570091412</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.585862222737264</v>
+        <v>4.083059687953178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.6098355650901794</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.090689570091412</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.585862389455472</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.2253624945878983</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.585862586486082</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3949376344680786</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.585862427345974</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5712899565696716</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.585862465236476</v>
+        <v>4.08305993045239</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4742701053619385</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.585862662267086</v>
+        <v>4.083060127483001</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.2838486433029175</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.585862639532785</v>
+        <v>4.0830601047487</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3490907251834869</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.585862487970777</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4505905508995056</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.585862412189773</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.3960681557655334</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.585862510705079</v>
+        <v>4.083059975920994</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.572166383266449</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1496946894453832</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.585862518283179</v>
+        <v>4.083059983499094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.3488650321960449</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.090689570091412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.585862783516693</v>
+        <v>4.083060248732608</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5451099872589111</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.090689570091412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.585862487970777</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5974142551422119</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.090689570091412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.585862730469989</v>
+        <v>4.083060195685905</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.2027894854545593</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.090689570091412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.585862813829094</v>
+        <v>4.083060279045009</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.7553636431694031</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.585862647110886</v>
+        <v>4.083060112326801</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2139192670583725</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.3496946894453832</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.585862836563396</v>
+        <v>4.083060301779311</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3220082819461823</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.585862487970777</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3455816805362701</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.585862283362066</v>
+        <v>4.083059748577981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3924161493778229</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.585862397033572</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.1995196640491486</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.585862412189773</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4108869135379791</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.585862177268662</v>
+        <v>4.083059642484576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.2264077514410019</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.585862237893464</v>
+        <v>4.083059703109379</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4886841177940369</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.1496946894453832</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.585862109065757</v>
+        <v>4.083059574281672</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.7032046318054199</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.585862245471565</v>
+        <v>4.08305971068748</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4621877670288086</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.585862419767873</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2539445161819458</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.391300191200645</v>
+        <v>0.3</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.585862563751781</v>
+        <v>4.083060028967696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4078121185302734</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.391300191200645</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.585862397033572</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.141048401594162</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.585862389455472</v>
+        <v>4.083059854671387</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.349381685256958</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.585862101487657</v>
+        <v>4.083059566703572</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5895230174064636</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.3496946894453832</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.585862116643858</v>
+        <v>4.083059581859773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.349298357963562</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.090689570091412</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.58586234398687</v>
+        <v>4.083059809202784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.5469629168510437</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.3496946894453832</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.585862328830669</v>
+        <v>4.083059794046584</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.1579428315162659</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3496946894453832</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.585862434924075</v>
+        <v>4.08305990013999</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4006970822811127</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.58586216211246</v>
+        <v>4.083059627328375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.5391224026679993</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.3496946894453832</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.585862260627765</v>
+        <v>4.08305972584368</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3962314128875732</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.585862412189773</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4169079065322876</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.585862427345974</v>
+        <v>4.083059892561889</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4249836206436157</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.585862404611673</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4730395972728729</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.3</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.585862487970777</v>
+        <v>4.083059953186692</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3273274302482605</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.585862586486082</v>
+        <v>4.083060051701997</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2831591069698334</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.585862419767873</v>
+        <v>4.083059884983788</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3793299794197083</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.585862404611673</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3310202360153198</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.585862374299271</v>
+        <v>4.083059839515186</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4218118786811829</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.585862359143071</v>
+        <v>4.083059824358986</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3959363400936127</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.591300191200645</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.585862397033572</v>
+        <v>4.083059862249487</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3771668076515198</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.585862412189773</v>
+        <v>4.083059877405688</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.3713731467723846</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.591300191200645</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.585862404611673</v>
+        <v>4.083059869827588</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_3_000007.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000007.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.4303023219108582</v>
+        <v>0.4303023815155029</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.58</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.4540941417217255</v>
+        <v>0.4540941715240479</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.4399999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.3832265436649323</v>
+        <v>0.3832264542579651</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.1600000000000001</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.4190527200698853</v>
+        <v>0.41905277967453</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.3</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4540854692459106</v>
+        <v>0.4540855884552002</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.4122450053691864</v>
+        <v>0.4122450649738312</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.7199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.4209644496440887</v>
+        <v>0.4209645092487335</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.4399999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.4131742417812347</v>
+        <v>0.4131743311882019</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.7199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.4808005392551422</v>
+        <v>0.480800598859787</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.7199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.3757018148899078</v>
+        <v>0.3757018446922302</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.4129667282104492</v>
+        <v>0.4129667580127716</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.473054438829422</v>
+        <v>0.4730545282363892</v>
       </c>
       <c r="JB18" t="n">
         <v>0.02000000000000007</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.4047074317932129</v>
+        <v>0.4047074615955353</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.4316766262054443</v>
+        <v>0.4316766858100891</v>
       </c>
       <c r="JB20" t="n">
         <v>0.5799999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.5506709218025208</v>
+        <v>0.5506709814071655</v>
       </c>
       <c r="JB21" t="n">
         <v>0.5799999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.568362832069397</v>
+        <v>0.5683628916740417</v>
       </c>
       <c r="JB22" t="n">
         <v>0.5799999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.6086592078208923</v>
+        <v>0.6086592674255371</v>
       </c>
       <c r="JB23" t="n">
         <v>0.5799999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.414949357509613</v>
+        <v>0.4149494469165802</v>
       </c>
       <c r="JB24" t="n">
         <v>0.4399999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.4448352158069611</v>
+        <v>0.4448353052139282</v>
       </c>
       <c r="JB25" t="n">
         <v>0.16</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.4428650140762329</v>
+        <v>0.4428650438785553</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.4134869277477264</v>
+        <v>0.4134870171546936</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.4004087448120117</v>
+        <v>0.4004088044166565</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.5672252178192139</v>
+        <v>0.5672253370285034</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3919841349124908</v>
+        <v>0.391984224319458</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.4392345547676086</v>
+        <v>0.4392346143722534</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4149449169635773</v>
+        <v>0.4149450063705444</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.3415319919586182</v>
+        <v>0.3415320515632629</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4548394680023193</v>
+        <v>0.4548395276069641</v>
       </c>
       <c r="JB34" t="n">
         <v>0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.4698078036308289</v>
+        <v>0.469807893037796</v>
       </c>
       <c r="JB35" t="n">
         <v>0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.6041152477264404</v>
+        <v>0.60411536693573</v>
       </c>
       <c r="JB36" t="n">
         <v>0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.7457963824272156</v>
+        <v>0.7457960844039917</v>
       </c>
       <c r="JB37" t="n">
         <v>0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.4919728934764862</v>
+        <v>0.4919727742671967</v>
       </c>
       <c r="JB38" t="n">
         <v>0.7199999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.5806690454483032</v>
+        <v>0.5806693434715271</v>
       </c>
       <c r="JB39" t="n">
         <v>0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.3628858327865601</v>
+        <v>0.3628861010074615</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.49091637134552</v>
+        <v>0.4909165799617767</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.16</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.5133123993873596</v>
+        <v>0.5133124589920044</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.16</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.6741918921470642</v>
+        <v>0.6741923093795776</v>
       </c>
       <c r="JB43" t="n">
         <v>0.1199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.7892181277275085</v>
+        <v>0.789218544960022</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.7580748796463013</v>
+        <v>0.7580755949020386</v>
       </c>
       <c r="JB45" t="n">
         <v>0.7199999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.621149480342865</v>
+        <v>0.6211510300636292</v>
       </c>
       <c r="JB46" t="n">
         <v>0.4399999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.414670318365097</v>
+        <v>0.4146707952022552</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.3</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.1608821600675583</v>
+        <v>0.160882756114006</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.4399999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.570720911026001</v>
+        <v>0.5707212090492249</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.5038540959358215</v>
+        <v>0.503854513168335</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.2761980295181274</v>
+        <v>0.2761981785297394</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.7199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.3609869778156281</v>
+        <v>0.3609872758388519</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.8599999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.4447287023067474</v>
+        <v>0.4447288811206818</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.4263668358325958</v>
+        <v>0.4263670146465302</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.7199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.5437252521514893</v>
+        <v>0.543725311756134</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.7199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.4825732707977295</v>
+        <v>0.4825735092163086</v>
       </c>
       <c r="JB56" t="n">
         <v>0.16</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.8801813721656799</v>
+        <v>0.8801819086074829</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.1199999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.4378393590450287</v>
+        <v>0.4378402829170227</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.1199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.301520973443985</v>
+        <v>0.3015212714672089</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.4835888147354126</v>
+        <v>0.4835889637470245</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.280401736497879</v>
+        <v>0.2804020047187805</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.7199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.3616936206817627</v>
+        <v>0.3616938591003418</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.4399999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.7170830965042114</v>
+        <v>0.7170833945274353</v>
       </c>
       <c r="JB64" t="n">
         <v>0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.9131059050559998</v>
+        <v>0.9131063222885132</v>
       </c>
       <c r="JB65" t="n">
         <v>0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.9469486474990845</v>
+        <v>0.9469493627548218</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.2820963859558105</v>
+        <v>0.2820983231067657</v>
       </c>
       <c r="JB67" t="n">
         <v>0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.2045919299125671</v>
+        <v>0.2045928239822388</v>
       </c>
       <c r="JB68" t="n">
         <v>0.02000000000000007</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.5172472596168518</v>
+        <v>0.5172479748725891</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.8599999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.4815314412117004</v>
+        <v>0.4815320372581482</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.8599999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.2886600196361542</v>
+        <v>0.2886602580547333</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.8599999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.2943706810474396</v>
+        <v>0.2943708896636963</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.2577203512191772</v>
+        <v>0.2577205896377563</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.2921161651611328</v>
+        <v>0.2921163439750671</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.3960876762866974</v>
+        <v>0.3960878252983093</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.356293112039566</v>
+        <v>0.356293261051178</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.3693419396877289</v>
+        <v>0.3693419992923737</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.2237703800201416</v>
+        <v>0.2237704694271088</v>
       </c>
       <c r="JB78" t="n">
         <v>0.16</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.6212947964668274</v>
+        <v>0.6212949752807617</v>
       </c>
       <c r="JB79" t="n">
         <v>0.1600000000000001</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.6098355650901794</v>
+        <v>0.6098358631134033</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1600000000000001</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.2253624945878983</v>
+        <v>0.2253626734018326</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.3949376344680786</v>
+        <v>0.3949376940727234</v>
       </c>
       <c r="JB82" t="n">
         <v>0.3</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.5712899565696716</v>
+        <v>0.571290135383606</v>
       </c>
       <c r="JB83" t="n">
         <v>0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.4742701053619385</v>
+        <v>0.4742705821990967</v>
       </c>
       <c r="JB84" t="n">
         <v>0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.2838486433029175</v>
+        <v>0.283848911523819</v>
       </c>
       <c r="JB85" t="n">
         <v>0.3</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.3490907251834869</v>
+        <v>0.3490908443927765</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.5799999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.4505905508995056</v>
+        <v>0.4505906403064728</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.3960681557655334</v>
+        <v>0.3960683047771454</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.4399999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.572166383266449</v>
+        <v>0.5721668004989624</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.3488650321960449</v>
+        <v>0.3488653600215912</v>
       </c>
       <c r="JB90" t="n">
         <v>0.4399999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.5451099872589111</v>
+        <v>0.5451101660728455</v>
       </c>
       <c r="JB91" t="n">
         <v>0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.5974142551422119</v>
+        <v>0.5974146127700806</v>
       </c>
       <c r="JB92" t="n">
         <v>0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.2027894854545593</v>
+        <v>0.202789694070816</v>
       </c>
       <c r="JB93" t="n">
         <v>0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.7553636431694031</v>
+        <v>0.7553643584251404</v>
       </c>
       <c r="JB94" t="n">
         <v>0.1600000000000001</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.2139192670583725</v>
+        <v>0.2139196991920471</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.3220082819461823</v>
+        <v>0.3220086097717285</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.3455816805362701</v>
+        <v>0.3455817699432373</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.1995196640491486</v>
+        <v>0.1995197832584381</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.4108869135379791</v>
+        <v>0.4108870029449463</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.4886841177940369</v>
+        <v>0.4886840581893921</v>
       </c>
       <c r="JB102" t="n">
         <v>0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.7032046318054199</v>
+        <v>0.703204870223999</v>
       </c>
       <c r="JB103" t="n">
         <v>0.4399999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.4621877670288086</v>
+        <v>0.4621878564357758</v>
       </c>
       <c r="JB104" t="n">
         <v>0.5799999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.2539445161819458</v>
+        <v>0.2539445459842682</v>
       </c>
       <c r="JB105" t="n">
         <v>0.3</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.4078121185302734</v>
+        <v>0.407812237739563</v>
       </c>
       <c r="JB106" t="n">
         <v>0.02000000000000007</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.141048401594162</v>
+        <v>0.141048476099968</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.5799999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.5895230174064636</v>
+        <v>0.5895228981971741</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.4399999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.349298357963562</v>
+        <v>0.3492984175682068</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.4399999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.5469629168510437</v>
+        <v>0.5469629764556885</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.3</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.1579428315162659</v>
+        <v>0.157942920923233</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.3962314128875732</v>
+        <v>0.3962314426898956</v>
       </c>
       <c r="JB115" t="n">
         <v>0.3</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4169079065322876</v>
+        <v>0.41690793633461</v>
       </c>
       <c r="JB116" t="n">
         <v>0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.4249836206436157</v>
+        <v>0.4249836504459381</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.4730395972728729</v>
+        <v>0.4730397164821625</v>
       </c>
       <c r="JB118" t="n">
         <v>0.3</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.2831591069698334</v>
+        <v>0.2831591665744781</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.3793299794197083</v>
+        <v>0.3793300092220306</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.8599999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.3310202360153198</v>
+        <v>0.3310202658176422</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.4218118786811829</v>
+        <v>0.4218119084835052</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.3771668076515198</v>
+        <v>0.3771668970584869</v>
       </c>
       <c r="JB125" t="n">
         <v>0.1600000000000001</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.3713731467723846</v>
+        <v>0.371373325586319</v>
       </c>
       <c r="JB126" t="n">
         <v>0.1600000000000001</v>
